--- a/financial_advisor_forms/015_personal_finance_tracker--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/015_personal_finance_tracker--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bi_weekly</t>
+          <t>bi weekly</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>on_track</t>
+          <t>on track</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>off_track</t>
+          <t>off track</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>on_track</t>
+          <t>on track</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>off_track</t>
+          <t>off track</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>on_track</t>
+          <t>on track</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>off_track</t>
+          <t>off track</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>not_submitted</t>
+          <t>not submitted</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pending_review</t>
+          <t>pending review</t>
         </is>
       </c>
     </row>
